--- a/80_Threshold_OUTPUT_REPORT/best_conclusion_data.xlsx
+++ b/80_Threshold_OUTPUT_REPORT/best_conclusion_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/80_Threshold_OUTPUT_REPORT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0676E6-335F-974D-8074-DD0DC6516EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911F644D-2754-C042-92A8-77B89AF71ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
